--- a/Schemas/ISO9001_2015.xlsx
+++ b/Schemas/ISO9001_2015.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alvih\OneDrive\Documents\LearningCodeProjects\AuditNotesWebSite\Schemas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/4e7b105ed33480c9/AuditorSpace_Empty/SchemaTemplates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F79266F5-F79E-4236-9E61-0497C60C9F74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{F79266F5-F79E-4236-9E61-0497C60C9F74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{853A5521-6876-4609-81D6-D4C6FFB4EC0E}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -447,11 +447,11 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -749,610 +749,610 @@
       </c>
     </row>
     <row r="2" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="6">
+      <c r="A2" s="5">
         <v>1</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="6" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="6">
+      <c r="A3" s="5">
         <v>2</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="6" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="6">
+      <c r="A4" s="5">
         <v>3</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="6" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="6">
+      <c r="A5" s="5">
         <v>4</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="6" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="6">
+      <c r="A6" s="5">
         <v>4.0999999999999996</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="6" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="6">
+      <c r="A7" s="5">
         <v>4.2</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="6" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="6">
+      <c r="A8" s="5">
         <v>4.3</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="6" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="6">
+      <c r="A9" s="5">
         <v>4.4000000000000004</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="6" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="6">
+      <c r="A10" s="5">
         <v>5</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="6" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="6">
+      <c r="A11" s="5">
         <v>5.0999999999999996</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="6" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="6" t="s">
+      <c r="A12" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B12" s="6" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="6" t="s">
+      <c r="A13" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B13" s="6" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="6">
+      <c r="A14" s="5">
         <v>5.2</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="B14" s="6" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="6" t="s">
+      <c r="A15" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="B15" s="6" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="16" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="6" t="s">
+      <c r="A16" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="B16" s="5" t="s">
+      <c r="B16" s="6" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="6">
+      <c r="A17" s="5">
         <v>5.3</v>
       </c>
-      <c r="B17" s="5" t="s">
+      <c r="B17" s="6" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="6">
+      <c r="A18" s="5">
         <v>6</v>
       </c>
-      <c r="B18" s="5" t="s">
+      <c r="B18" s="6" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="6">
+      <c r="A19" s="5">
         <v>6.1</v>
       </c>
-      <c r="B19" s="5" t="s">
+      <c r="B19" s="6" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="6">
+      <c r="A20" s="5">
         <v>6.2</v>
       </c>
-      <c r="B20" s="5" t="s">
+      <c r="B20" s="6" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="6">
+      <c r="A21" s="5">
         <v>6.3</v>
       </c>
-      <c r="B21" s="5" t="s">
+      <c r="B21" s="6" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="22" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="6">
+      <c r="A22" s="5">
         <v>7</v>
       </c>
-      <c r="B22" s="5" t="s">
+      <c r="B22" s="6" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="23" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="6">
+      <c r="A23" s="5">
         <v>7.1</v>
       </c>
-      <c r="B23" s="5" t="s">
+      <c r="B23" s="6" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="24" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="6" t="s">
+      <c r="A24" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="B24" s="5" t="s">
+      <c r="B24" s="6" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="25" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="6" t="s">
+      <c r="A25" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="B25" s="5" t="s">
+      <c r="B25" s="6" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="26" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="6" t="s">
+      <c r="A26" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="B26" s="5" t="s">
+      <c r="B26" s="6" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="27" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="6" t="s">
+      <c r="A27" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="B27" s="5" t="s">
+      <c r="B27" s="6" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="28" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="6" t="s">
+      <c r="A28" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="B28" s="5" t="s">
+      <c r="B28" s="6" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="29" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="6" t="s">
+      <c r="A29" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="B29" s="5" t="s">
+      <c r="B29" s="6" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="30" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="6">
+      <c r="A30" s="5">
         <v>7.2</v>
       </c>
-      <c r="B30" s="5" t="s">
+      <c r="B30" s="6" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="31" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="6">
+      <c r="A31" s="5">
         <v>7.3</v>
       </c>
-      <c r="B31" s="5" t="s">
+      <c r="B31" s="6" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="32" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="6">
+      <c r="A32" s="5">
         <v>7.4</v>
       </c>
-      <c r="B32" s="5" t="s">
+      <c r="B32" s="6" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="33" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="6">
+      <c r="A33" s="5">
         <v>7.5</v>
       </c>
-      <c r="B33" s="5" t="s">
+      <c r="B33" s="6" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="34" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="6" t="s">
+      <c r="A34" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="B34" s="5" t="s">
+      <c r="B34" s="6" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="35" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A35" s="6" t="s">
+      <c r="A35" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="B35" s="5" t="s">
+      <c r="B35" s="6" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="36" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="6" t="s">
+      <c r="A36" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="B36" s="5" t="s">
+      <c r="B36" s="6" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="37" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="6">
+      <c r="A37" s="5">
         <v>8</v>
       </c>
-      <c r="B37" s="5" t="s">
+      <c r="B37" s="6" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="38" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="6">
+      <c r="A38" s="5">
         <v>8.1</v>
       </c>
-      <c r="B38" s="5" t="s">
+      <c r="B38" s="6" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="39" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="6">
+      <c r="A39" s="5">
         <v>8.1999999999999993</v>
       </c>
-      <c r="B39" s="5" t="s">
+      <c r="B39" s="6" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="40" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="6" t="s">
+      <c r="A40" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="B40" s="5" t="s">
+      <c r="B40" s="6" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="41" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A41" s="6" t="s">
+      <c r="A41" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="B41" s="5" t="s">
+      <c r="B41" s="6" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="42" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A42" s="6" t="s">
+      <c r="A42" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="B42" s="5" t="s">
+      <c r="B42" s="6" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="43" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A43" s="6" t="s">
+      <c r="A43" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="B43" s="5" t="s">
+      <c r="B43" s="6" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="44" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="6">
+      <c r="A44" s="5">
         <v>8.3000000000000007</v>
       </c>
-      <c r="B44" s="5" t="s">
+      <c r="B44" s="6" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="45" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A45" s="6" t="s">
+      <c r="A45" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="B45" s="5" t="s">
+      <c r="B45" s="6" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="46" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A46" s="6" t="s">
+      <c r="A46" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="B46" s="5" t="s">
+      <c r="B46" s="6" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="47" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A47" s="6" t="s">
+      <c r="A47" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="B47" s="5" t="s">
+      <c r="B47" s="6" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="48" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A48" s="6" t="s">
+      <c r="A48" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="B48" s="5" t="s">
+      <c r="B48" s="6" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="49" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A49" s="6" t="s">
+      <c r="A49" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="B49" s="5" t="s">
+      <c r="B49" s="6" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="50" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A50" s="6" t="s">
+      <c r="A50" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="B50" s="5" t="s">
+      <c r="B50" s="6" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="51" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A51" s="6">
+    <row r="51" spans="1:2" ht="27.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A51" s="5">
         <v>8.4</v>
       </c>
-      <c r="B51" s="5" t="s">
+      <c r="B51" s="6" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="52" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A52" s="6" t="s">
+      <c r="A52" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="B52" s="5" t="s">
+      <c r="B52" s="6" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="53" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A53" s="6" t="s">
+      <c r="A53" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="B53" s="5" t="s">
+      <c r="B53" s="6" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="54" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A54" s="6" t="s">
+      <c r="A54" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="B54" s="5" t="s">
+      <c r="B54" s="6" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="55" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A55" s="6">
+      <c r="A55" s="5">
         <v>8.5</v>
       </c>
-      <c r="B55" s="5" t="s">
+      <c r="B55" s="6" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="56" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A56" s="6" t="s">
+      <c r="A56" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="B56" s="5" t="s">
+      <c r="B56" s="6" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="57" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A57" s="6" t="s">
+      <c r="A57" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="B57" s="5" t="s">
+      <c r="B57" s="6" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="58" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A58" s="6" t="s">
+      <c r="A58" s="5" t="s">
         <v>92</v>
       </c>
-      <c r="B58" s="5" t="s">
+      <c r="B58" s="6" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="59" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A59" s="6" t="s">
+      <c r="A59" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="B59" s="5" t="s">
+      <c r="B59" s="6" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="60" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A60" s="6" t="s">
+      <c r="A60" s="5" t="s">
         <v>96</v>
       </c>
-      <c r="B60" s="5" t="s">
+      <c r="B60" s="6" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="61" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A61" s="6" t="s">
+      <c r="A61" s="5" t="s">
         <v>98</v>
       </c>
-      <c r="B61" s="5" t="s">
+      <c r="B61" s="6" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="62" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A62" s="6">
+      <c r="A62" s="5">
         <v>8.6</v>
       </c>
-      <c r="B62" s="5" t="s">
+      <c r="B62" s="6" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="63" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A63" s="6">
+      <c r="A63" s="5">
         <v>8.6999999999999993</v>
       </c>
-      <c r="B63" s="5" t="s">
+      <c r="B63" s="6" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="64" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A64" s="6">
+      <c r="A64" s="5">
         <v>9</v>
       </c>
-      <c r="B64" s="5" t="s">
+      <c r="B64" s="6" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="65" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A65" s="6">
+      <c r="A65" s="5">
         <v>9.1</v>
       </c>
-      <c r="B65" s="5" t="s">
+      <c r="B65" s="6" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="66" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A66" s="6" t="s">
+      <c r="A66" s="5" t="s">
         <v>103</v>
       </c>
-      <c r="B66" s="5" t="s">
+      <c r="B66" s="6" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="67" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A67" s="6" t="s">
+      <c r="A67" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="B67" s="5" t="s">
+      <c r="B67" s="6" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="68" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A68" s="6" t="s">
+      <c r="A68" s="5" t="s">
         <v>106</v>
       </c>
-      <c r="B68" s="5" t="s">
+      <c r="B68" s="6" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="69" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A69" s="6">
+      <c r="A69" s="5">
         <v>9.1999999999999993</v>
       </c>
-      <c r="B69" s="5" t="s">
+      <c r="B69" s="6" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="70" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A70" s="6">
+      <c r="A70" s="5">
         <v>9.3000000000000007</v>
       </c>
-      <c r="B70" s="5" t="s">
+      <c r="B70" s="6" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="71" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A71" s="6" t="s">
+      <c r="A71" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="B71" s="5" t="s">
+      <c r="B71" s="6" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="72" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A72" s="6" t="s">
+      <c r="A72" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="B72" s="5" t="s">
+      <c r="B72" s="6" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="73" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A73" s="6" t="s">
+      <c r="A73" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="B73" s="5" t="s">
+      <c r="B73" s="6" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="74" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A74" s="6">
+      <c r="A74" s="5">
         <v>10</v>
       </c>
-      <c r="B74" s="5" t="s">
+      <c r="B74" s="6" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="75" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A75" s="6">
+      <c r="A75" s="5">
         <v>10.1</v>
       </c>
-      <c r="B75" s="5" t="s">
+      <c r="B75" s="6" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="76" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A76" s="6">
+      <c r="A76" s="5">
         <v>10.199999999999999</v>
       </c>
-      <c r="B76" s="5" t="s">
+      <c r="B76" s="6" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="77" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A77" s="6">
+      <c r="A77" s="5">
         <v>10.3</v>
       </c>
-      <c r="B77" s="5" t="s">
+      <c r="B77" s="6" t="s">
         <v>35</v>
       </c>
     </row>
